--- a/2026_B题/outputs/result.xlsx
+++ b/2026_B题/outputs/result.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>481.5</v>
+        <v>481.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>482</v>
+        <v>482.2</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>510.2</v>
+        <v>510.6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>511.7</v>
+        <v>512.1</v>
       </c>
     </row>
     <row r="16">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -911,7 +911,6 @@
         <v>763.5</v>
       </c>
     </row>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026_B题/outputs/result.xlsx
+++ b/2026_B题/outputs/result.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -476,24 +476,8 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" t="n">
         <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>476.5</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>477</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -506,24 +490,8 @@
       <c r="L2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>477</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>477.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -553,11 +521,11 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -566,10 +534,10 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>481</v>
+        <v>476.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>481.5</v>
+        <v>477</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -593,11 +561,11 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -606,10 +574,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>481.7</v>
+        <v>477</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>482.2</v>
+        <v>477.5</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -619,11 +587,11 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -632,19 +600,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>488.4</v>
+        <v>481</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>488.9</v>
+        <v>481.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -653,19 +621,19 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>492.6</v>
+        <v>481.5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>493.1</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -674,19 +642,19 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>493.1</v>
+        <v>488.4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>493.6</v>
+        <v>488.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -695,19 +663,19 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>493.6</v>
+        <v>492.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>494.1</v>
+        <v>493.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -716,19 +684,19 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>494.1</v>
+        <v>493.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>494.6</v>
+        <v>493.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -737,40 +705,40 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>494.6</v>
+        <v>493.6</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>495.1</v>
+        <v>494.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>507.2</v>
+        <v>494.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>508.7</v>
+        <v>494.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -779,103 +747,103 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>508.8</v>
+        <v>494.6</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>509.3</v>
+        <v>495.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>模拟射击</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>509.3</v>
+        <v>507.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>509.8</v>
+        <v>508.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>510.6</v>
+        <v>508.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>512.1</v>
+        <v>509.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>513.4</v>
+        <v>509.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>514.9</v>
+        <v>510.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>模拟射击</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>750.3</v>
+        <v>510.6</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>750.8</v>
+        <v>512.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -884,30 +852,72 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>751</v>
+        <v>513.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>752.5</v>
+        <v>514.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>750.3</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>750.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>模拟射击</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>751</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>752.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>S13</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>模拟射击</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D21" s="4" t="n">
         <v>762</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>763.5</v>
       </c>
     </row>

--- a/2026_B题/outputs/result.xlsx
+++ b/2026_B题/outputs/result.xlsx
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>481.5</v>
+        <v>481.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>482</v>
+        <v>482.2</v>
       </c>
     </row>
     <row r="8">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>509.8</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>510.3</v>
       </c>
     </row>
     <row r="17">
@@ -822,7 +822,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>510.6</v>
+        <v>510.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>512.1</v>
+        <v>511.7</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">

--- a/2026_B题/outputs/result.xlsx
+++ b/2026_B题/outputs/result.xlsx
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>481.5</v>
+        <v>481.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>482</v>
+        <v>482.2</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">

--- a/2026_B题/outputs/result.xlsx
+++ b/2026_B题/outputs/result.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>481.7</v>
+        <v>481.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>482.2</v>
+        <v>482</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
